--- a/paginas_encontradas.xlsx
+++ b/paginas_encontradas.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,21 +413,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C205"/>
+  <dimension ref="A1:C131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Serie</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Busqueda</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
@@ -448,3468 +436,2210 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://maps.google.com/maps?sca_esv=b95b1b9f09dfb697&amp;output=search&amp;q=%22El+Bot%C3%ADn%22+Uruguay+site:instagram.com&amp;source=lnms&amp;fbs=ADc_l-bpk8W4E-qsVlOvbGJcDwpn60DczFdcvPnuv8WQohHLTaMb_WtLz8zQ41bNqiqMK_2tAHCL8fGF2xU6_n5bwc1VlYlRTUOwh1dpsTwTvnfgK_WBqr-YTGjv-AmP1dWPD6XL4rEnxOZSad7brYEOuVNumnJ0Pp-YeN5SEQ4dAXUON7uJ2gia5TLi8HtiXOx9idJ02yO6T0puj0koGQdFbMX1wp4-2w&amp;entry=mc&amp;ved=1t:200715&amp;ictx=111</t>
+          <t>https://www.instagram.com/tctelevision/p/DVORrImDeBs/?hl=af</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.google.com/travel/flights?sca_esv=b95b1b9f09dfb697&amp;output=search&amp;q=%22El+Bot%C3%ADn%22+Uruguay+site:instagram.com&amp;source=lnms&amp;fbs=ADc_l-bpk8W4E-qsVlOvbGJcDwpn60DczFdcvPnuv8WQohHLTaMb_WtLz8zQ41bNqiqMK_2tAHCL8fGF2xU6_n5bwc1VlYlRTUOwh1dpsTwTvnfgK_WBqr-YTGjv-AmP1dWPD6XL4rEnxOZSad7brYEOuVNumnJ0Pp-YeN5SEQ4dAXUON7uJ2gia5TLi8HtiXOx9idJ02yO6T0puj0koGQdFbMX1wp4-2w&amp;ved=1t:200715&amp;ictx=111</t>
+          <t>https://www.instagram.com/p/DVOz-rogGXC/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.google.com/finance?sca_esv=b95b1b9f09dfb697&amp;output=search&amp;q=%22El+Bot%C3%ADn%22+Uruguay+site:instagram.com&amp;source=lnms&amp;fbs=ADc_l-bpk8W4E-qsVlOvbGJcDwpn60DczFdcvPnuv8WQohHLTaMb_WtLz8zQ41bNqiqMK_2tAHCL8fGF2xU6_n5bwc1VlYlRTUOwh1dpsTwTvnfgK_WBqr-YTGjv-AmP1dWPD6XL4rEnxOZSad7brYEOuVNumnJ0Pp-YeN5SEQ4dAXUON7uJ2gia5TLi8HtiXOx9idJ02yO6T0puj0koGQdFbMX1wp4-2w&amp;sa=X&amp;ved=2ahUKEwje2pWuxoKTAxUr7skDHTbiJ6kQ0pQJegQIQRAB</t>
+          <t>https://www.instagram.com/p/DVOSgCPkZjd/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DVPky0zEckJ/</t>
+          <t>https://www.instagram.com/p/DVOdiylkRc-/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DVUvf9ViXZl/</t>
+          <t>https://www.instagram.com/p/DVMpuBIgEgM/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DS-ViSCDmgH/</t>
+          <t>https://www.instagram.com/p/DVMSBXUj67w/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DVRu4vKiQpe/</t>
+          <t>https://www.instagram.com/p/DVMdRG4iYyX/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DTv-yLPlMoN/</t>
+          <t>https://www.instagram.com/p/DUGzvSKCcYb/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DURRRtaFW3i/</t>
+          <t>https://www.instagram.com/p/DSvPPdWkTwb/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/C3nQl0WuA80/</t>
+          <t>https://www.instagram.com/p/DUycL_tDOVR/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DT9ndvRDTGf/</t>
+          <t>https://www.instagram.com/p/DUPD4U9Dj3H/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DT12S7wF5gI/</t>
+          <t>https://www.instagram.com/p/DSyG11PF-B4/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DTvQmvaEfNS/</t>
+          <t>https://www.instagram.com/reel/DVE-d1EibtV/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DTsSnzBgunO/</t>
+          <t>https://www.instagram.com/p/DUGpQq-ET9_/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DVTWRjNkafI/</t>
+          <t>https://www.instagram.com/reel/DUUbJnADa1G/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DJuxiTaKzEL/</t>
+          <t>https://www.instagram.com/p/DVPsr7HjUQR/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DGx9mMkP36m/</t>
+          <t>https://www.instagram.com/p/DUJlHkvkbJu/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DJutEnxg2Wn/</t>
+          <t>https://www.instagram.com/p/DUHgZlgEQG_/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/C37F2oGuBeP/</t>
+          <t>https://www.instagram.com/p/DTvwrTAEWuh/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DUbUMs3kfKz/</t>
+          <t>https://www.instagram.com/p/DVST-buDMPt/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.google.com/finance?sca_esv=b95b1b9f09dfb697&amp;output=search&amp;q=%22El+Bot%C3%ADn%22+Uruguay+site:instagram.com&amp;source=lnms&amp;fbs=ADc_l-bpk8W4E-qsVlOvbGJcDwpn60DczFdcvPnuv8WQohHLTaMb_WtLz8zQ41bNqiqMK_2tAHCL8fGF2xU6_n5bwc1VlYlRTUOwh1dpsTwTvnfgK_WBqr-YTGjv-AmP1dWPD6XL4rEnxOZSad7brYEOuVNumnJ0Pp-YeN5SEQ4dAXUON7uJ2gia5TLi8HtiXOx9idJ02yO6T0puj0koGQdFbMX1wp4-2w&amp;sa=X&amp;ved=2ahUKEwjFmbqzxoKTAxXGa_EDHebTO084ChDSlAl6BAg3EAE</t>
+          <t>https://www.instagram.com/p/DUlEx1NjaYZ/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DTzZJI9AA9R/</t>
+          <t>https://www.instagram.com/p/DUGyD-6j4ls/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DUBiCwwDe1C/</t>
+          <t>https://www.instagram.com/p/DUJH2TEDHrY/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DOHoeI_CkAT/</t>
+          <t>https://www.instagram.com/p/DSu-BlzEYzy/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/popular/el-bot%C3%ADn-netflix-reparto/</t>
+          <t>https://www.instagram.com/p/DUGftZ0jrum/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/C-u6J3kJIZf/</t>
+          <t>https://www.instagram.com/p/DVPLEs_DodX/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DOOXDKxE35k/</t>
+          <t>https://www.instagram.com/p/DS5geZTDU8R/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DURTADZD28s/</t>
+          <t>https://www.instagram.com/p/DUUOAlgj70E/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DTLWC3hkX6G/</t>
+          <t>https://www.instagram.com/netflixlat/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DUJps1XDwiC/</t>
+          <t>https://www.instagram.com/p/DVZEA-EjAVg/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/popular/el-botin-netflix-cuando-se-estrena/</t>
+          <t>https://www.facebook.com/NetflixArg/videos/bridgerton-netflix/874579312061852/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DUJbWlvjaGA/</t>
+          <t>https://www.facebook.com/cadenadelmarfm1065/videos/bridgerton-netflix-4%C2%AA-temporada-arrasa-y-vuelve-a-cautivar-al-p%C3%BAblico/2171927366915739/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://www.google.com/finance?sca_esv=b95b1b9f09dfb697&amp;output=search&amp;q=%22El+Bot%C3%ADn%22+Uruguay+site:instagram.com&amp;source=lnms&amp;fbs=ADc_l-bpk8W4E-qsVlOvbGJcDwpn60DczFdcvPnuv8WQohHLTaMb_WtLz8zQ41bNqiqMK_2tAHCL8fGF2xU6_n5bwc1VlYlRTUOwh1dpsTwTvnfgK_WBqr-YTGjv-AmP1dWPD6XL4rEnxOZSad7brYEOuVNumnJ0Pp-YeN5SEQ4dAXUON7uJ2gia5TLi8HtiXOx9idJ02yO6T0puj0koGQdFbMX1wp4-2w&amp;sa=X&amp;ved=2ahUKEwj7npq5xoKTAxXXSPEDHWWhG_o4FBDSlAl6BAgyEAE</t>
+          <t>https://www.facebook.com/ComfortUruguay/videos/una-nueva-pista-perfumada-llega-al-palacioel-secreto-est%C3%A1-a-punto-de-ser-revelad/1615445112706598/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DTEBPREktmD/</t>
+          <t>https://www.facebook.com/NetflixArg/videos/bridgerton-netflix/2378705162590136/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DQUp6J_Aotm/</t>
+          <t>https://www.facebook.com/cartasaeliza/posts/ya-sabes-a-qu%C3%A9-hora-estar%C3%A1n-disponibles-los-nuevos-episodios-de-bridgerton-estad/1512664910859722/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DUBmvMDiJRU/</t>
+          <t>https://www.facebook.com/groups/769572330299468/posts/1762034177719940/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DTQV8UyEW6v/</t>
+          <t>https://www.facebook.com/NetflixArg/videos/bridgerton-netflix/887334047385646/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DRuYSmIka5G/</t>
+          <t>https://www.facebook.com/NetflixArg/videos/bridgerton-netflix/742416995394439/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DNePiVaJRbW/</t>
+          <t>https://www.facebook.com/debateuruguaynoticias/posts/baile-de-m%C3%A1scaras-y-taylor-swift-se-estren%C3%B3-la-cuarta-temporada-de-los-bridgerto/877969608319032/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DObHByoDqty/</t>
+          <t>https://www.facebook.com/NetflixArg/videos/bridgerton-netflix/1472684427721945/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DR0XB0NkfCx/</t>
+          <t>https://www.facebook.com/NetflixArg/posts/este-es-el-evento-de-la-temporada-para-todos-los-fans-de-bridgertonel-9-de-febre/1330235185804528/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DT-7UaLDcV8/</t>
+          <t>https://www.facebook.com/elpaisuy/posts/de-bridgerton-a-la-odisea-de-nolan-y-hasta-una-pel%C3%ADcula-uruguaya-sobre-escritora/1232928072301948/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DUTsbJ0Ebbt/</t>
+          <t>https://www.facebook.com/vovediariodigital/posts/-la-espera-de-los-fan%C3%A1ticos-de-bridgerton-llega-a-su-fin-finalmente-este-jueves-/1219537233704696/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://maps.google.com/maps?sca_esv=b95b1b9f09dfb697&amp;output=search&amp;q=%22El+Bot%C3%ADn%22+Uruguay+site:facebook.com&amp;source=lnms&amp;fbs=ADc_l-bpk8W4E-qsVlOvbGJcDwpn60DczFdcvPnuv8WQohHLTaMb_WtLz8zQ41bNqiqMK_2tAHCL8fGF2xU6_n5bwc1VlYlRTUOwh1dpsTwTvnfgK_WBqr-YTGjv-AmP1dWPD6XL4rEnxOZSad7brYEOuVNumnJ0Pp-YeN5SEQ4dAXUON7uJ2gia5TLi8HtiXOx9idJ02yO6T0puj0koGQdFbMX1wp4-2w&amp;entry=mc&amp;ved=1t:200715&amp;ictx=111</t>
+          <t>https://www.facebook.com/clarincom/posts/la-cuarta-temporada-debuta-este-29-de-enero-en-netflix-para-desentra%C3%B1ar-el-inici/1341408221354182/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.google.com/travel/flights?sca_esv=b95b1b9f09dfb697&amp;output=search&amp;q=%22El+Bot%C3%ADn%22+Uruguay+site:facebook.com&amp;source=lnms&amp;fbs=ADc_l-bpk8W4E-qsVlOvbGJcDwpn60DczFdcvPnuv8WQohHLTaMb_WtLz8zQ41bNqiqMK_2tAHCL8fGF2xU6_n5bwc1VlYlRTUOwh1dpsTwTvnfgK_WBqr-YTGjv-AmP1dWPD6XL4rEnxOZSad7brYEOuVNumnJ0Pp-YeN5SEQ4dAXUON7uJ2gia5TLi8HtiXOx9idJ02yO6T0puj0koGQdFbMX1wp4-2w&amp;ved=1t:200715&amp;ictx=111</t>
+          <t>https://www.facebook.com/RTSmedios/photos/espect%C3%A1culos-netflix-revel%C3%B3-t%C3%ADtulos-y-duraci%C3%B3n-de-los-primeros-episodios-de-la-c/1369331881873630/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://www.google.com/finance?sca_esv=b95b1b9f09dfb697&amp;output=search&amp;q=%22El+Bot%C3%ADn%22+Uruguay+site:facebook.com&amp;source=lnms&amp;fbs=ADc_l-bpk8W4E-qsVlOvbGJcDwpn60DczFdcvPnuv8WQohHLTaMb_WtLz8zQ41bNqiqMK_2tAHCL8fGF2xU6_n5bwc1VlYlRTUOwh1dpsTwTvnfgK_WBqr-YTGjv-AmP1dWPD6XL4rEnxOZSad7brYEOuVNumnJ0Pp-YeN5SEQ4dAXUON7uJ2gia5TLi8HtiXOx9idJ02yO6T0puj0koGQdFbMX1wp4-2w&amp;sa=X&amp;ved=2ahUKEwjpzPe-xoKTAxUPVPEDHUruNUIQ0pQJegQIPRAB</t>
+          <t>https://www.facebook.com/ComfortUruguay/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/elpaisuy/posts/el-bot%C3%ADn-es-la-pel%C3%ADcula-m%C3%A1s-vista-de-netflix-en-uruguay-este-martes-20-de-enero-/1238138185114270/</t>
+          <t>https://www.facebook.com/libreriaelvirreyuy/posts/tras-la-exitosa-saga-bridgerton-que-netflix-ha-convertido-en-una-serie-llega-la-/2858888594376833/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/photo.php?fbid=1237961358465286&amp;set=a.535916288669800&amp;id=100067543011103</t>
+          <t>https://www.facebook.com/photo.php?fbid=1747795425302901&amp;id=299859170096541&amp;set=a.299860116763113</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/elpaisuy/posts/en-la-pel%C3%ADcula-m%C3%A1s-vista-por-los-uruguayos-en-netflix-hoy-el-descubrimiento-de-v/1237961398465282/</t>
+          <t>https://www.facebook.com/elpaisuy/posts/netflix-revel%C3%B3-el-primer-adelanto-de-la-cuarta-temporada-de-bridgerton-y-confirm/1161703156091107/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/visionariord/videos/desde-nuestro-escritorio-asi-se-escribio-la-historia-en-el-2005-uruguay-el-bot%C3%ADn/1814225072761070/</t>
+          <t>https://www.facebook.com/ElObservadorUY/posts/bridgerton-fue-una-de-las-series-m%C3%A1s-vistas-en-netflix-el-verano-pasado-en-urugu/10159849239625842/?locale=hi_IN</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/CLPortal.UY/posts/el-bot%C3%ADn-el-regreso-de-dos-estrellas-de-hollywood-en-un-intenso-thriller-crimina/878513164929990/</t>
+          <t>https://www.facebook.com/ComfortUruguay/videos/las-flores-desaparecieron-de-manera-misteriosa-el-secreto-m%C3%A1s-perfumado-podr%C3%A1-se/25344967681849805/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tvshowuy/posts/el-bot%C3%ADn-el-regreso-de-dos-estrellas-de-hollywood-en-un-intenso-thriller-crimina/1580963106837682/</t>
+          <t>https://www.facebook.com/NetflixArg/videos/bridgerton-netflix/863898726412695/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/PasqualiniUruguay/videos/ya-conoc%C3%A9s-el-bot%C3%ADn-trama-encontralo-en-tiendas-y-web-/1092722465559018/</t>
+          <t>https://www.facebook.com/NetflixArg/videos/bridgerton-netflix/888088347102338/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/zapateriaelbotin/</t>
+          <t>https://www.facebook.com/tvshowuy/posts/m%C3%A1s-oscura-y-melanc%C3%B3lica-detalles-de-la-temporada-4-de-bridgerton-y-cu%C3%A1ndo-se-es/1585824876351505/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/269257664654388/posts/1170901967823282/</t>
+          <t>https://www.facebook.com/perfilcom/posts/a-qu%C3%A9-hora-se-estren%C3%B3-en-netflix-la-segunda-parte-de-bridgerton-4-en-argentina/1353904796770185/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/cadenadelmarfm1065/posts/tras-una-r%C3%A1pida-intervenci%C3%B3n-de-las-unidades-de-patrullaje-las-autoridades-logra/1700674814720264/</t>
+          <t>https://www.facebook.com/ComfortUruguay/videos/las-flores-desaparecieron-de-manera-misteriosa-el-secreto-m%C3%A1s-perfumado-podr%C3%A1-se/893079166830234/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.google.com/finance?sca_esv=b95b1b9f09dfb697&amp;output=search&amp;q=%22El+Bot%C3%ADn%22+Uruguay+site:facebook.com&amp;source=lnms&amp;fbs=ADc_l-bpk8W4E-qsVlOvbGJcDwpn60DczFdcvPnuv8WQohHLTaMb_WtLz8zQ41bNqiqMK_2tAHCL8fGF2xU6_n5bwc1VlYlRTUOwh1dpsTwTvnfgK_WBqr-YTGjv-AmP1dWPD6XL4rEnxOZSad7brYEOuVNumnJ0Pp-YeN5SEQ4dAXUON7uJ2gia5TLi8HtiXOx9idJ02yO6T0puj0koGQdFbMX1wp4-2w&amp;sa=X&amp;ved=2ahUKEwiWoq7DxoKTAxVbxMkDHcvOFvQ4ChDSlAl6BAg0EAE</t>
+          <t>https://www.facebook.com/NetflixArg/videos/bridgerton-3-parte-2/448650128016965/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/photo.php?fbid=472069809666111&amp;id=112079815665114&amp;set=a.112083912331371&amp;locale=ku_TR</t>
+          <t>https://www.facebook.com/elpaisuy/posts/netflix-asegura-que-bridgerton-es-la-serie-m%C3%A1s-vista-de-toda-su-historia-la-prod/10160662759376754/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/2011343276009575/posts/2151652788645289/</t>
+          <t>https://www.facebook.com/NetflixArg/videos/bridgerton-3-parte-2/464109322937601/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/zapateriaelbotin/?locale=es_LA</t>
+          <t>https://www.facebook.com/groups/769572330299468/posts/1727394321183926/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/zapateriaelbotin/?locale=sq_AL</t>
+          <t>https://www.facebook.com/elpaisuy/photos/netflix-revel%C3%B3-el-primer-adelanto-de-la-cuarta-temporada-de-bridgerton-y-confirm/1161703139424442/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/815018978591104/posts/25519557681043891/</t>
+          <t>https://www.facebook.com/redessocialesarg/videos/un-paseo-estilo-bridgerton-gratis-en-buenos-aires-s%C3%AD-est%C3%A1-pasandonetflix-organiz/926751779827211/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ladiaria/posts/por-fin-una-historia-socialista-suplementocultura/10160446673226182/</t>
+          <t>https://www.facebook.com/elpaisuy/posts/netflix-asegura-que-bridgerton-es-la-serie-m%C3%A1s-vista-de-toda-su-historia-la-prod/10160660939456754/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/1635435016741849/posts/2215387972079881/</t>
+          <t>https://www.tiktok.com/@chenetflix/video/7600424191522786573</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/61559956925251/posts/uruguay-se-lleva-el-bot%C3%ADn-con-poca-claridad-pero-aprovechando-los-errores-de-col/122145869108331897/</t>
+          <t>https://www.tiktok.com/@milakate1999/video/7606732930806729991</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/zapateriaelbotin/?locale=fa_IR</t>
+          <t>https://www.tiktok.com/@netflixlat/video/7593055754735865096</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/invenciblesalto/posts/bot%C3%ADn-n%C3%A1poles-acompa%C3%B1%C3%A1ndote-en-cada-paso-que-dascl%C3%A1sico-urbano-con-alma-de-campo/1139813721281399/</t>
+          <t>https://www.tiktok.com/@netflixlat/video/7602268274629397776</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/elpaisuy/photos/en-la-pel%C3%ADcula-m%C3%A1s-vista-por-los-uruguayos-en-netflix-hoy-el-descubrimiento-de-v/1237961358465286/</t>
+          <t>https://www.tiktok.com/@chenetflix/video/7595703870014131469</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://m.facebook.com/100080313945224/photos/708553508498441/</t>
+          <t>https://www.tiktok.com/@chenetflix/video/7609844795061652749</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/CatLifestyleUruguay/posts/new-arrivals-si-busc%C3%A1s-estilo-y-comodidad-el-bot%C3%ADn-stats-es-ideal-para-vos-encon/936297823243305/</t>
+          <t>https://www.tiktok.com/@netflixes/video/7600447840447581462</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/garimport/photos/protecci%C3%B3n-y-confort-en-cada-paso-el-bot%C3%ADn-miura-es-ideal-para-el-trabajo-profes/1207216011413232/</t>
+          <t>https://www.tiktok.com/@chenetflix/video/7595649570139344142</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://maps.google.com/maps?sca_esv=aacf70bb308dc659&amp;output=search&amp;q=%22El+Bot%C3%ADn%22+Uruguay+site:facebook.com&amp;source=lnms&amp;fbs=ADc_l-bpk8W4E-qsVlOvbGJcDwpn60DczFdcvPnuv8WQohHLTaMb_WtLz8zQ41bNqiqMK_2tAHCL8fGF2xU6_n5bwc1VlYlRTUOwh1dpsTwTvnfgK_WBqr-YTGjv-AmP1dWPD6XL4rEnxOZSad7brYEOuVNumnJ0Pp-YeN5SEQ4dAXUON7uJ2gia5TLi8HtiXOx9idJ02yO6T0puj0koGQdFbMX1wp4-2w&amp;entry=mc&amp;ved=1t:200715&amp;ictx=111</t>
+          <t>https://www.tiktok.com/@eugepuche/video/7611298973923495176</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://www.google.com/travel/flights?sca_esv=aacf70bb308dc659&amp;output=search&amp;q=%22El+Bot%C3%ADn%22+Uruguay+site:facebook.com&amp;source=lnms&amp;fbs=ADc_l-bpk8W4E-qsVlOvbGJcDwpn60DczFdcvPnuv8WQohHLTaMb_WtLz8zQ41bNqiqMK_2tAHCL8fGF2xU6_n5bwc1VlYlRTUOwh1dpsTwTvnfgK_WBqr-YTGjv-AmP1dWPD6XL4rEnxOZSad7brYEOuVNumnJ0Pp-YeN5SEQ4dAXUON7uJ2gia5TLi8HtiXOx9idJ02yO6T0puj0koGQdFbMX1wp4-2w&amp;ved=1t:200715&amp;ictx=111</t>
+          <t>https://www.tiktok.com/@pijama.surf/video/7600861625373035796</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://www.google.com/finance?sca_esv=aacf70bb308dc659&amp;output=search&amp;q=%22El+Bot%C3%ADn%22+Uruguay+site:facebook.com&amp;source=lnms&amp;fbs=ADc_l-bpk8W4E-qsVlOvbGJcDwpn60DczFdcvPnuv8WQohHLTaMb_WtLz8zQ41bNqiqMK_2tAHCL8fGF2xU6_n5bwc1VlYlRTUOwh1dpsTwTvnfgK_WBqr-YTGjv-AmP1dWPD6XL4rEnxOZSad7brYEOuVNumnJ0Pp-YeN5SEQ4dAXUON7uJ2gia5TLi8HtiXOx9idJ02yO6T0puj0koGQdFbMX1wp4-2w&amp;sa=X&amp;ved=2ahUKEwjKv9XIxoKTAxVn5MkDHYcsHYE4FBDSlAl6BAg2EAE</t>
+          <t>https://www.tiktok.com/discover/cuando-sale-bridgerton-4-en-argentina</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ladiaria/photos/a.416511066181/10160007218746182/?type=3&amp;locale=ms_MY</t>
+          <t>https://www.tiktok.com/@netflixlat/video/7369335819200449793</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://hi-in.facebook.com/elpaisuy/photos/a.435549706753/10161558609096754/?type=3</t>
+          <t>https://www.tiktok.com/@netflixlat/video/7603930655117872404</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/zapateriaelbotin/?locale=be_BY</t>
+          <t>https://www.tiktok.com/@chenetflix/video/7598326974951607565</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ladiaria/posts/la-obra-futbolera-recorre-los-momentos-fundacionales-del-deporte-en-nuestro-pa%C3%ADs/1410195204451670/</t>
+          <t>https://www.tiktok.com/@chenetflix/video/7601155903466851598</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/zapateriaelbotin/?locale=ur_PK</t>
+          <t>https://www.tiktok.com/@topic.media/video/7394894841613683973</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/crhoy.comnoticias/posts/el-bot%C3%ADn-sustra%C3%ADdo-en-pa%C3%ADs-sudamericano-ronda-los-3-millones/2166877440021278/?locale=es_LA</t>
+          <t>https://www.tiktok.com/@cpher_art/video/7609546888773127445</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/zapateriaelbotin/?locale=gl_ES</t>
+          <t>https://www.tiktok.com/@chenetflix/video/7610098651112705294</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/edmundo.andrus/posts/unos-pocos-se-llevan-el-bot%C3%ADn-y-nosotros-lo-pagamos-as%C3%AD-es-la-justicia-uruguaya/1236274348504487/</t>
+          <t>https://www.tiktok.com/@apasionadosxviajar/video/7609550112158764309</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/zapateriaelbotin/?locale=pa_IN</t>
+          <t>https://www.tiktok.com/@marcoseyo/video/7601633663150722311</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/61557516163772/photos/122145392102250538/</t>
+          <t>https://www.tiktok.com/@chulaenlaluna/video/7600849139949112583</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/HushPuppiesUY/posts/olv%C3%ADdate-del-cansancio-al-caminar-con-el-bot%C3%ADn-fu-gracias-a-sus-componentes-y-co/554348476792979/</t>
+          <t>https://www.tiktok.com/@chenetflix/video/7358085398805007658</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/garimport/photos/a.286829184672284/3535998589755311/?type=3</t>
+          <t>https://www.tiktok.com/@mariaspeaksenglish/video/7369691983713094945</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/textilshop.uy/posts/-pis%C3%A1-fuerte-con-esta-promo-el-bot%C3%ADn-kempo-es-resistente-y-muuuy-c%C3%B3modo-y-est%C3%A1-a/3471541986279161/</t>
+          <t>https://www.tiktok.com/@netflixes/video/7367679551809277216</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:facebook.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/61557516163772/photos/122149577474250538/</t>
+          <t>https://www.tiktok.com/@alewkd/video/7367172113842654470</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://maps.google.com/maps?sca_esv=b95b1b9f09dfb697&amp;output=search&amp;q=%22El+Bot%C3%ADn%22+Uruguay+site:tiktok.com&amp;source=lnms&amp;fbs=ADc_l-bpk8W4E-qsVlOvbGJcDwpn60DczFdcvPnuv8WQohHLTaMb_WtLz8zQ41bNqiqMK_2tAHCL8fGF2xU6_n5bwc1VlYlRTUOwh1dpsTwTvnfgK_WBqr-YTGjv-AmP1dWPD6XL4rEnxOZSad7brYEOuVNumnJ0Pp-YeN5SEQ4dAXUON7uJ2gia5TLi8HtiXOx9idJ02yO6T0puj0koGQdFbMX1wp4-2w&amp;entry=mc&amp;ved=1t:200715&amp;ictx=111</t>
+          <t>https://www.tiktok.com/discover/bridgerton-argentina-victoria-resco</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://www.google.com/travel/flights?sca_esv=b95b1b9f09dfb697&amp;output=search&amp;q=%22El+Bot%C3%ADn%22+Uruguay+site:tiktok.com&amp;source=lnms&amp;fbs=ADc_l-bpk8W4E-qsVlOvbGJcDwpn60DczFdcvPnuv8WQohHLTaMb_WtLz8zQ41bNqiqMK_2tAHCL8fGF2xU6_n5bwc1VlYlRTUOwh1dpsTwTvnfgK_WBqr-YTGjv-AmP1dWPD6XL4rEnxOZSad7brYEOuVNumnJ0Pp-YeN5SEQ4dAXUON7uJ2gia5TLi8HtiXOx9idJ02yO6T0puj0koGQdFbMX1wp4-2w&amp;ved=1t:200715&amp;ictx=111</t>
+          <t>https://www.tiktok.com/@chenetflix/video/7606441973901233422</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://www.google.com/finance?sca_esv=b95b1b9f09dfb697&amp;output=search&amp;q=%22El+Bot%C3%ADn%22+Uruguay+site:tiktok.com&amp;source=lnms&amp;fbs=ADc_l-bpk8W4E-qsVlOvbGJcDwpn60DczFdcvPnuv8WQohHLTaMb_WtLz8zQ41bNqiqMK_2tAHCL8fGF2xU6_n5bwc1VlYlRTUOwh1dpsTwTvnfgK_WBqr-YTGjv-AmP1dWPD6XL4rEnxOZSad7brYEOuVNumnJ0Pp-YeN5SEQ4dAXUON7uJ2gia5TLi8HtiXOx9idJ02yO6T0puj0koGQdFbMX1wp4-2w&amp;sa=X&amp;ved=2ahUKEwjcm7XNxoKTAxXS5MkDHRllFNoQ0pQJegQILRAB</t>
+          <t>https://www.tiktok.com/@adriianabad99/video/7601432071604702487</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@omeletelatam/video/7597137099539664148</t>
+          <t>https://www.tiktok.com/@suny.jks/video/7603162089301003528</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@costicine/video/7599274212167306499</t>
+          <t>https://www.youtube.com/watch?v=IAqV-7F-brg</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@accesoilimitado/video/7594645337499847956</t>
+          <t>https://www.youtube.com/watch?v=0NSWp5airvo</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cinevirgo88/video/7605913236306677010</t>
+          <t>https://www.youtube.com/watch?v=UsAEQwTAuH0</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@futboldeleyendass/video/7571063969499286786</t>
+          <t>https://www.youtube.com/hashtag/staircasescene</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/discover/el-bot%C3%ADn-netflix-entrevista-en-espa%C3%B1ol</t>
+          <t>https://www.youtube.com/c/aragondigital/channels</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@paul_salas_z/video/7531611706238307592</t>
+          <t>https://www.youtube.com/watch?v=kMXQlA14JBQ</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@elbpublicidadmx/video/7598293006449462536</t>
+          <t>https://m.youtube.com/@LADSpanishTV-8386x/videos?view=0&amp;sort=dd&amp;shelf_id=2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/discover/el-botin-historia-real-de-vuela-vuelanetflix</t>
+          <t>https://x.com/DebateUruguay_/status/2017275931405258915</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@luchocomedi/video/7583380729191714069</t>
+          <t>https://x.com/agusc4brera</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://www.google.com/finance?sca_esv=b95b1b9f09dfb697&amp;output=search&amp;q=%22El+Bot%C3%ADn%22+Uruguay+site:tiktok.com&amp;source=lnms&amp;fbs=ADc_l-bpk8W4E-qsVlOvbGJcDwpn60DczFdcvPnuv8WQohHLTaMb_WtLz8zQ41bNqiqMK_2tAHCL8fGF2xU6_n5bwc1VlYlRTUOwh1dpsTwTvnfgK_WBqr-YTGjv-AmP1dWPD6XL4rEnxOZSad7brYEOuVNumnJ0Pp-YeN5SEQ4dAXUON7uJ2gia5TLi8HtiXOx9idJ02yO6T0puj0koGQdFbMX1wp4-2w&amp;sa=X&amp;ved=2ahUKEwibmtvSxoKTAxUYVPEDHX4nAvE4ChDSlAl6BAgoEAE</t>
+          <t>https://x.com/elpaisuy/status/1344705160375894019</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@roberto_cparra/video/7597482287801928980</t>
+          <t>https://x.com/vicky_oyhenart</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fiorellalarosa_/video/7242456171016113413</t>
+          <t>https://x.com/proximapaginaok</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@medio_pique/video/7399049137028680965</t>
+          <t>https://x.com/XimeCoonX</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@feriauno/video/7595942133870120213</t>
+          <t>https://x.com/nadia2abi</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@dans.apartment/video/7548507537436429586</t>
+          <t>https://x.com/karenreiscach</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chelseamaey/video/7213272705850805509</t>
+          <t>https://x.com/lizkocacomert</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@futbolactualizado_/video/7536689135017266437</t>
+          <t>https://x.com/NBonin/status/1797486263148396771</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/discover/quien-es-dayo-en-la-pel%C3%ADcula-el-botin</t>
+          <t>https://x.com/arissanchezzz</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@criterio.hn/video/7115222441143684358</t>
+          <t>https://x.com/__lavenderhaze</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@eltiosneakersuy/video/7498470849645726981</t>
+          <t>https://x.com/anto_z31</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@guayosas/video/7509666701001231622</t>
+          <t>https://x.com/feer__olvv</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cecytoriz/video/7432527047609584901</t>
+          <t>https://x.com/laboraton</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@deykobella/video/7328191521335823622</t>
+          <t>https://x.com/mpazperalta</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@west.montana/video/7602728210937187592</t>
+          <t>https://x.com/Jotadangz</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@botineslaplata/video/7565857989622582529</t>
+          <t>https://x.com/Gala0374</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://www.google.com/finance?sca_esv=b95b1b9f09dfb697&amp;output=search&amp;q=%22El+Bot%C3%ADn%22+Uruguay+site:tiktok.com&amp;source=lnms&amp;fbs=ADc_l-bpk8W4E-qsVlOvbGJcDwpn60DczFdcvPnuv8WQohHLTaMb_WtLz8zQ41bNqiqMK_2tAHCL8fGF2xU6_n5bwc1VlYlRTUOwh1dpsTwTvnfgK_WBqr-YTGjv-AmP1dWPD6XL4rEnxOZSad7brYEOuVNumnJ0Pp-YeN5SEQ4dAXUON7uJ2gia5TLi8HtiXOx9idJ02yO6T0puj0koGQdFbMX1wp4-2w&amp;sa=X&amp;ved=2ahUKEwi3uavYxoKTAxXewckDHVocBdw4FBDSlAl6BAglEAE</t>
+          <t>https://x.com/puig_vero</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@break_yam_/video/7229816905798831365</t>
+          <t>https://x.com/search?q=%23OCCH%C4%B0AM%C4%B0N&amp;src=typed_query</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@elkiko12/video/7263997402447744262</t>
+          <t>https://x.com/newslinereport</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@latinus_us/video/7206702930269834501</t>
+          <t>https://x.com/lecturasdeannie</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cheunmateoficial/video/7573837042317102347</t>
+          <t>https://x.com/MaugeGarcia</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@uribedj/video/7596038456581573895</t>
+          <t>https://x.com/florenciaamorin</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@sieteleguasoriginal/video/7565599980430380296</t>
+          <t>https://x.com/ddl_sophie97</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ale.justel/video/7603961936547466516</t>
+          <t>https://x.com/lys_12</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@calzadosmorelly/video/7533297491245255942</t>
+          <t>https://x.com/Aurorakillian30</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@toqueyrebote/video/7556662773921451276</t>
+          <t>https://x.com/Manuu_CYfan</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@blackbootsmx/video/7594639856584674581</t>
+          <t>https://x.com/search?lang=es&amp;q=Sigue%20plataforma%20DUTT%20comentarios%202026%20usuarios%20reales.uns</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hacheproperu/video/7574946841448549639</t>
+          <t>https://x.com/nazagaggero</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>El Botín</t>
+          <t>Bridgerton</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@limalimonpitalito/video/7379775482499222789</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@7k.safety.peru/video/7377026980480290054</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@solobotinesfutbol/video/7349920003413527814</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:tiktok.com</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@historiasdelarealidadbo/video/7383082443709926689</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>https://maps.google.com/maps?sca_esv=b95b1b9f09dfb697&amp;output=search&amp;q=%22El+Bot%C3%ADn%22+Uruguay+site:youtube.com&amp;source=lnms&amp;fbs=ADc_l-bpk8W4E-qsVlOvbGJcDwpn60DczFdcvPnuv8WQohHLTaMb_WtLz8zQ41bNqiqMK_2tAHCL8fGF2xU6_n5bwc1VlYlRTUOwh1dpsTwTvnfgK_WBqr-YTGjv-AmP1dWPD6XL4rEnxOZSad7brYEOuVNumnJ0Pp-YeN5SEQ4dAXUON7uJ2gia5TLi8HtiXOx9idJ02yO6T0puj0koGQdFbMX1wp4-2w&amp;entry=mc&amp;ved=1t:200715&amp;ictx=111</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>https://www.google.com/travel/flights?sca_esv=b95b1b9f09dfb697&amp;output=search&amp;q=%22El+Bot%C3%ADn%22+Uruguay+site:youtube.com&amp;source=lnms&amp;fbs=ADc_l-bpk8W4E-qsVlOvbGJcDwpn60DczFdcvPnuv8WQohHLTaMb_WtLz8zQ41bNqiqMK_2tAHCL8fGF2xU6_n5bwc1VlYlRTUOwh1dpsTwTvnfgK_WBqr-YTGjv-AmP1dWPD6XL4rEnxOZSad7brYEOuVNumnJ0Pp-YeN5SEQ4dAXUON7uJ2gia5TLi8HtiXOx9idJ02yO6T0puj0koGQdFbMX1wp4-2w&amp;ved=1t:200715&amp;ictx=111</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>https://www.google.com/finance?sca_esv=b95b1b9f09dfb697&amp;output=search&amp;q=%22El+Bot%C3%ADn%22+Uruguay+site:youtube.com&amp;source=lnms&amp;fbs=ADc_l-bpk8W4E-qsVlOvbGJcDwpn60DczFdcvPnuv8WQohHLTaMb_WtLz8zQ41bNqiqMK_2tAHCL8fGF2xU6_n5bwc1VlYlRTUOwh1dpsTwTvnfgK_WBqr-YTGjv-AmP1dWPD6XL4rEnxOZSad7brYEOuVNumnJ0Pp-YeN5SEQ4dAXUON7uJ2gia5TLi8HtiXOx9idJ02yO6T0puj0koGQdFbMX1wp4-2w&amp;sa=X&amp;ved=2ahUKEwi09KnexoKTAxV74ckDHaqhEn0Q0pQJegQIMxAB</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=PofkPyuGaSw</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=virY3UBWb6Q</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=QWC9_O6fcD4</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=Jtj5uqvVoWQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=XYuH_u-I0i8</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=w0EXU3me_SY</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=6e5_ekTQCeE</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>https://m.youtube.com/watch?v=fT0pXZC_mNA</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=3kEaryTT-HM</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=NSw1H5AW_Y4</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>https://www.google.com/finance?sca_esv=b95b1b9f09dfb697&amp;output=search&amp;q=%22El+Bot%C3%ADn%22+Uruguay+site:youtube.com&amp;source=lnms&amp;fbs=ADc_l-bpk8W4E-qsVlOvbGJcDwpn60DczFdcvPnuv8WQohHLTaMb_WtLz8zQ41bNqiqMK_2tAHCL8fGF2xU6_n5bwc1VlYlRTUOwh1dpsTwTvnfgK_WBqr-YTGjv-AmP1dWPD6XL4rEnxOZSad7brYEOuVNumnJ0Pp-YeN5SEQ4dAXUON7uJ2gia5TLi8HtiXOx9idJ02yO6T0puj0koGQdFbMX1wp4-2w&amp;sa=X&amp;ved=2ahUKEwjD4-jlxoKTAxU8cvEDHU01BF84ChDSlAl6BAgnEAE</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=WQI9naDS1JE</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=H5RqlzvtLTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=qilX8zdbGRk</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=L9ZwZrAzmds</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=FYwoIvLFYMc</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=kY2nFWxaaAg</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=gskqUqntLjM</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=IFJqxSAFvro</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=yCP7HABdBxI</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=bU8eweCU9BU</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>https://www.google.com/finance?sca_esv=b95b1b9f09dfb697&amp;output=search&amp;q=%22El+Bot%C3%ADn%22+Uruguay+site:youtube.com&amp;source=lnms&amp;fbs=ADc_l-bpk8W4E-qsVlOvbGJcDwpn60DczFdcvPnuv8WQohHLTaMb_WtLz8zQ41bNqiqMK_2tAHCL8fGF2xU6_n5bwc1VlYlRTUOwh1dpsTwTvnfgK_WBqr-YTGjv-AmP1dWPD6XL4rEnxOZSad7brYEOuVNumnJ0Pp-YeN5SEQ4dAXUON7uJ2gia5TLi8HtiXOx9idJ02yO6T0puj0koGQdFbMX1wp4-2w&amp;sa=X&amp;ved=2ahUKEwiP2_TrxoKTAxV_SvEDHYmOLs84FBDSlAl6BAgpEAE</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=WPCZAkWCKXY</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=2QUNLw2d-g4</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=TvvTaqxVB2Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/playlist?list=PLj6MhMI3ahDIc--hpzxBDpHbY-bvBz_jy</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=Ws5u1nshzqg</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=p2u7mXNl05Q</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=_aG5HJOxOQQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=gPqx5pSFemQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=RpEIgW0bqw4</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:youtube.com</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=zeYBFebElvo</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>https://maps.google.com/maps?sca_esv=b95b1b9f09dfb697&amp;output=search&amp;q=%22El+Bot%C3%ADn%22+Uruguay+site:x.com&amp;source=lnms&amp;fbs=ADc_l-bpk8W4E-qsVlOvbGJcDwpn60DczFdcvPnuv8WQohHLTaMb_WtLz8zQ41bNqiqMK_2tAHCL8fGF2xU6_n5bwc1VlYlRTUOwh1dpsTwTvnfgK_WBqr-YTGjv-AmP1dWPD6XL4rEnxOZSad7brYEOuVNumnJ0Pp-YeN5SEQ4dAXUON7uJ2gia5TLi8HtiXOx9idJ02yO6T0puj0koGQdFbMX1wp4-2w&amp;entry=mc&amp;ved=1t:200715&amp;ictx=111</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>https://www.google.com/travel/flights?sca_esv=b95b1b9f09dfb697&amp;output=search&amp;q=%22El+Bot%C3%ADn%22+Uruguay+site:x.com&amp;source=lnms&amp;fbs=ADc_l-bpk8W4E-qsVlOvbGJcDwpn60DczFdcvPnuv8WQohHLTaMb_WtLz8zQ41bNqiqMK_2tAHCL8fGF2xU6_n5bwc1VlYlRTUOwh1dpsTwTvnfgK_WBqr-YTGjv-AmP1dWPD6XL4rEnxOZSad7brYEOuVNumnJ0Pp-YeN5SEQ4dAXUON7uJ2gia5TLi8HtiXOx9idJ02yO6T0puj0koGQdFbMX1wp4-2w&amp;ved=1t:200715&amp;ictx=111</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>https://www.google.com/finance?sca_esv=b95b1b9f09dfb697&amp;output=search&amp;q=%22El+Bot%C3%ADn%22+Uruguay+site:x.com&amp;source=lnms&amp;fbs=ADc_l-bpk8W4E-qsVlOvbGJcDwpn60DczFdcvPnuv8WQohHLTaMb_WtLz8zQ41bNqiqMK_2tAHCL8fGF2xU6_n5bwc1VlYlRTUOwh1dpsTwTvnfgK_WBqr-YTGjv-AmP1dWPD6XL4rEnxOZSad7brYEOuVNumnJ0Pp-YeN5SEQ4dAXUON7uJ2gia5TLi8HtiXOx9idJ02yO6T0puj0koGQdFbMX1wp4-2w&amp;sa=X&amp;ved=2ahUKEwjVsq_xxoKTAxXVSPEDHYzLGEkQ0pQJegQIRBAB</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>https://x.com/ObservadorUY/status/1808627867854479478?lang=ar-x-fm</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>https://x.com/periodistan_/status/1155939511324381184?lang=el</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>https://x.com/PorLaRaya890/status/1954158479930712142</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>https://x.com/RoqueJCGarcia/status/1938871579099762708</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>https://x.com/qvlcda</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>https://x.com/marcelobotines</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>https://x.com/defogonenfogon</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>https://x.com/orvesays/status/1905791765333905795</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>https://x.com/bolsolocura49</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>https://x.com/emepege/status/2025297723638096197</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>https://x.com/_JoseVD</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>https://x.com/qvlcda/with_replies</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>https://www.google.com/finance?sca_esv=b95b1b9f09dfb697&amp;output=search&amp;q=%22El+Bot%C3%ADn%22+Uruguay+site:x.com&amp;source=lnms&amp;fbs=ADc_l-bpk8W4E-qsVlOvbGJcDwpn60DczFdcvPnuv8WQohHLTaMb_WtLz8zQ41bNqiqMK_2tAHCL8fGF2xU6_n5bwc1VlYlRTUOwh1dpsTwTvnfgK_WBqr-YTGjv-AmP1dWPD6XL4rEnxOZSad7brYEOuVNumnJ0Pp-YeN5SEQ4dAXUON7uJ2gia5TLi8HtiXOx9idJ02yO6T0puj0koGQdFbMX1wp4-2w&amp;sa=X&amp;ved=2ahUKEwiQ7cH3xoKTAxU3VPEDHX7WLQM4ChDSlAl6BAhFEAE</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>https://x.com/caalf01/status/1980764647952089270</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>https://x.com/tuccipa</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>https://x.com/elchemalistur</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>https://x.com/SirMoncha</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>https://x.com/sayaguesalberto?lang=cs</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>https://x.com/fabmellado</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>https://x.com/TheEdosama</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>https://x.com/LuisHer27313149</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>https://x.com/pablo_amestoy</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>https://x.com/mmachado15600/with_replies</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>https://x.com/pablo96molina</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>https://x.com/jmartinezjorge/status/2025177640940830979</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>https://x.com/guatavopallas</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>https://www.google.com/finance?sca_esv=b95b1b9f09dfb697&amp;output=search&amp;q=%22El+Bot%C3%ADn%22+Uruguay+site:x.com&amp;source=lnms&amp;fbs=ADc_l-bpk8W4E-qsVlOvbGJcDwpn60DczFdcvPnuv8WQohHLTaMb_WtLz8zQ41bNqiqMK_2tAHCL8fGF2xU6_n5bwc1VlYlRTUOwh1dpsTwTvnfgK_WBqr-YTGjv-AmP1dWPD6XL4rEnxOZSad7brYEOuVNumnJ0Pp-YeN5SEQ4dAXUON7uJ2gia5TLi8HtiXOx9idJ02yO6T0puj0koGQdFbMX1wp4-2w&amp;sa=X&amp;ved=2ahUKEwjWsM38xoKTAxVp1ckDHW6RH6Y4FBDSlAl6BAg9EAE</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>https://x.com/emanasliski</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>https://x.com/fabmellado/with_replies?lang=bn</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>https://x.com/leoelizeche</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>https://x.com/sebadh</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>https://x.com/agusposss</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>El Botín</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>"El Botín" Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>https://x.com/todosxuruguayok</t>
+          <t>https://x.com/tartancrepes</t>
         </is>
       </c>
     </row>

--- a/paginas_encontradas.xlsx
+++ b/paginas_encontradas.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,21 +425,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C131"/>
+  <dimension ref="A1:C129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Serie</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Busqueda</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
@@ -446,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tctelevision/p/DVORrImDeBs/?hl=af</t>
+          <t>https://www.instagram.com/p/DVOdiylkRc-/</t>
         </is>
       </c>
     </row>
@@ -463,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DVOz-rogGXC/</t>
+          <t>https://www.instagram.com/tctelevision/p/DVORrImDeBs/?hl=af</t>
         </is>
       </c>
     </row>
@@ -480,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DVOSgCPkZjd/</t>
+          <t>https://www.instagram.com/p/DVOz-rogGXC/</t>
         </is>
       </c>
     </row>
@@ -497,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DVOdiylkRc-/</t>
+          <t>https://www.instagram.com/p/DVOSgCPkZjd/</t>
         </is>
       </c>
     </row>
@@ -514,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DVMpuBIgEgM/</t>
+          <t>https://www.instagram.com/p/DJrtQepMxwi/</t>
         </is>
       </c>
     </row>
@@ -531,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DVMSBXUj67w/</t>
+          <t>https://www.instagram.com/p/DVMdRG4iYyX/</t>
         </is>
       </c>
     </row>
@@ -548,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DVMdRG4iYyX/</t>
+          <t>https://www.instagram.com/p/DT3FlgNDvHR/</t>
         </is>
       </c>
     </row>
@@ -565,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DUGzvSKCcYb/</t>
+          <t>https://www.instagram.com/p/DVMpuBIgEgM/</t>
         </is>
       </c>
     </row>
@@ -582,7 +594,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DSvPPdWkTwb/</t>
+          <t>https://www.instagram.com/p/DVPLEs_DodX/</t>
         </is>
       </c>
     </row>
@@ -599,7 +611,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DUycL_tDOVR/</t>
+          <t>https://www.instagram.com/p/DUHgZlgEQG_/</t>
         </is>
       </c>
     </row>
@@ -633,7 +645,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DSyG11PF-B4/</t>
+          <t>https://www.instagram.com/p/DUFea54DG6x/</t>
         </is>
       </c>
     </row>
@@ -667,7 +679,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DUGpQq-ET9_/</t>
+          <t>https://www.instagram.com/p/DSyG11PF-B4/</t>
         </is>
       </c>
     </row>
@@ -684,7 +696,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DUUbJnADa1G/</t>
+          <t>https://www.instagram.com/p/DUGpQq-ET9_/</t>
         </is>
       </c>
     </row>
@@ -735,7 +747,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DUHgZlgEQG_/</t>
+          <t>https://www.instagram.com/reel/DUUbJnADa1G/</t>
         </is>
       </c>
     </row>
@@ -752,7 +764,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DTvwrTAEWuh/</t>
+          <t>https://www.instagram.com/p/DVST-buDMPt/</t>
         </is>
       </c>
     </row>
@@ -769,7 +781,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DVST-buDMPt/</t>
+          <t>https://www.instagram.com/p/DSu-BlzEYzy/</t>
         </is>
       </c>
     </row>
@@ -786,7 +798,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DUlEx1NjaYZ/</t>
+          <t>https://www.instagram.com/p/DUGyD-6j4ls/</t>
         </is>
       </c>
     </row>
@@ -803,7 +815,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DUGyD-6j4ls/</t>
+          <t>https://www.instagram.com/p/DUlEx1NjaYZ/</t>
         </is>
       </c>
     </row>
@@ -820,7 +832,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DUJH2TEDHrY/</t>
+          <t>https://www.instagram.com/p/DS5geZTDU8R/</t>
         </is>
       </c>
     </row>
@@ -837,7 +849,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DSu-BlzEYzy/</t>
+          <t>https://www.instagram.com/p/DUJH2TEDHrY/</t>
         </is>
       </c>
     </row>
@@ -854,7 +866,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DUGftZ0jrum/</t>
+          <t>https://www.instagram.com/p/DUUOAlgj70E/</t>
         </is>
       </c>
     </row>
@@ -871,7 +883,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DVPLEs_DodX/</t>
+          <t>https://www.instagram.com/p/DStkvG1DEUY/</t>
         </is>
       </c>
     </row>
@@ -888,7 +900,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DS5geZTDU8R/</t>
+          <t>https://www.instagram.com/p/DSvW5bUEsoO/</t>
         </is>
       </c>
     </row>
@@ -900,12 +912,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DUUOAlgj70E/</t>
+          <t>https://www.facebook.com/NetflixArg/videos/bridgerton-netflix/874579312061852/</t>
         </is>
       </c>
     </row>
@@ -917,12 +929,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/netflixlat/</t>
+          <t>https://www.facebook.com/cadenadelmarfm1065/videos/bridgerton-netflix-4%C2%AA-temporada-arrasa-y-vuelve-a-cautivar-al-p%C3%BAblico/2171927366915739/</t>
         </is>
       </c>
     </row>
@@ -934,12 +946,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DVZEA-EjAVg/</t>
+          <t>https://www.facebook.com/ComfortUruguay/videos/una-nueva-pista-perfumada-llega-al-palacioel-secreto-est%C3%A1-a-punto-de-ser-revelad/1615445112706598/</t>
         </is>
       </c>
     </row>
@@ -956,7 +968,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/NetflixArg/videos/bridgerton-netflix/874579312061852/</t>
+          <t>https://www.facebook.com/NetflixArg/videos/bridgerton-netflix/2378705162590136/</t>
         </is>
       </c>
     </row>
@@ -973,7 +985,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/cadenadelmarfm1065/videos/bridgerton-netflix-4%C2%AA-temporada-arrasa-y-vuelve-a-cautivar-al-p%C3%BAblico/2171927366915739/</t>
+          <t>https://www.facebook.com/cartasaeliza/posts/ya-sabes-a-qu%C3%A9-hora-estar%C3%A1n-disponibles-los-nuevos-episodios-de-bridgerton-estad/1512664910859722/</t>
         </is>
       </c>
     </row>
@@ -990,7 +1002,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ComfortUruguay/videos/una-nueva-pista-perfumada-llega-al-palacioel-secreto-est%C3%A1-a-punto-de-ser-revelad/1615445112706598/</t>
+          <t>https://www.facebook.com/groups/769572330299468/posts/1762034177719940/</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1019,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/NetflixArg/videos/bridgerton-netflix/2378705162590136/</t>
+          <t>https://www.facebook.com/NetflixArg/videos/bridgerton-netflix/1472684427721945/</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1036,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/cartasaeliza/posts/ya-sabes-a-qu%C3%A9-hora-estar%C3%A1n-disponibles-los-nuevos-episodios-de-bridgerton-estad/1512664910859722/</t>
+          <t>https://www.facebook.com/NetflixArg/videos/bridgerton-netflix/742416995394439/</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1053,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/769572330299468/posts/1762034177719940/</t>
+          <t>https://www.facebook.com/debateuruguaynoticias/posts/baile-de-m%C3%A1scaras-y-taylor-swift-se-estren%C3%B3-la-cuarta-temporada-de-los-bridgerto/877969608319032/</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1087,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/NetflixArg/videos/bridgerton-netflix/742416995394439/</t>
+          <t>https://www.facebook.com/NetflixArg/posts/este-es-el-evento-de-la-temporada-para-todos-los-fans-de-bridgertonel-9-de-febre/1330235185804528/</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1104,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/debateuruguaynoticias/posts/baile-de-m%C3%A1scaras-y-taylor-swift-se-estren%C3%B3-la-cuarta-temporada-de-los-bridgerto/877969608319032/</t>
+          <t>https://www.facebook.com/NetflixArg/videos/bridgerton-netflix/1242972931091091/</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1121,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/NetflixArg/videos/bridgerton-netflix/1472684427721945/</t>
+          <t>https://www.facebook.com/elpaisuy/posts/de-bridgerton-a-la-odisea-de-nolan-y-hasta-una-pel%C3%ADcula-uruguaya-sobre-escritora/1232928072301948/</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1138,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/NetflixArg/posts/este-es-el-evento-de-la-temporada-para-todos-los-fans-de-bridgertonel-9-de-febre/1330235185804528/</t>
+          <t>https://www.facebook.com/vovediariodigital/posts/-la-espera-de-los-fan%C3%A1ticos-de-bridgerton-llega-a-su-fin-finalmente-este-jueves-/1219537233704696/</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1155,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/elpaisuy/posts/de-bridgerton-a-la-odisea-de-nolan-y-hasta-una-pel%C3%ADcula-uruguaya-sobre-escritora/1232928072301948/</t>
+          <t>https://www.facebook.com/RTSmedios/photos/espect%C3%A1culos-netflix-revel%C3%B3-t%C3%ADtulos-y-duraci%C3%B3n-de-los-primeros-episodios-de-la-c/1369331881873630/</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1172,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/vovediariodigital/posts/-la-espera-de-los-fan%C3%A1ticos-de-bridgerton-llega-a-su-fin-finalmente-este-jueves-/1219537233704696/</t>
+          <t>https://www.facebook.com/clarincom/posts/la-cuarta-temporada-debuta-este-29-de-enero-en-netflix-para-desentra%C3%B1ar-el-inici/1341408221354182/</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1189,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/clarincom/posts/la-cuarta-temporada-debuta-este-29-de-enero-en-netflix-para-desentra%C3%B1ar-el-inici/1341408221354182/</t>
+          <t>https://www.facebook.com/photo.php?fbid=1747795425302901&amp;id=299859170096541&amp;set=a.299860116763113</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1206,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/RTSmedios/photos/espect%C3%A1culos-netflix-revel%C3%B3-t%C3%ADtulos-y-duraci%C3%B3n-de-los-primeros-episodios-de-la-c/1369331881873630/</t>
+          <t>https://www.facebook.com/libreriaelvirreyuy/posts/tras-la-exitosa-saga-bridgerton-que-netflix-ha-convertido-en-una-serie-llega-la-/2858888594376833/</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1223,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ComfortUruguay/</t>
+          <t>https://www.facebook.com/ElObservadorUY/posts/bridgerton-fue-una-de-las-series-m%C3%A1s-vistas-en-netflix-el-verano-pasado-en-urugu/10159849239625842/?locale=hi_IN</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1240,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/libreriaelvirreyuy/posts/tras-la-exitosa-saga-bridgerton-que-netflix-ha-convertido-en-una-serie-llega-la-/2858888594376833/</t>
+          <t>https://www.facebook.com/elpaisuy/posts/netflix-revel%C3%B3-el-primer-adelanto-de-la-cuarta-temporada-de-bridgerton-y-confirm/1161703156091107/</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1257,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/photo.php?fbid=1747795425302901&amp;id=299859170096541&amp;set=a.299860116763113</t>
+          <t>https://www.facebook.com/NetflixArg/videos/bridgerton-netflix/888088347102338/</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1274,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/elpaisuy/posts/netflix-revel%C3%B3-el-primer-adelanto-de-la-cuarta-temporada-de-bridgerton-y-confirm/1161703156091107/</t>
+          <t>https://www.facebook.com/tvshowuy/posts/m%C3%A1s-oscura-y-melanc%C3%B3lica-detalles-de-la-temporada-4-de-bridgerton-y-cu%C3%A1ndo-se-es/1585824876351505/</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1291,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ElObservadorUY/posts/bridgerton-fue-una-de-las-series-m%C3%A1s-vistas-en-netflix-el-verano-pasado-en-urugu/10159849239625842/?locale=hi_IN</t>
+          <t>https://www.facebook.com/ComfortUruguay/videos/las-flores-desaparecieron-de-manera-misteriosa-el-secreto-m%C3%A1s-perfumado-podr%C3%A1-se/25344967681849805/</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1308,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ComfortUruguay/videos/las-flores-desaparecieron-de-manera-misteriosa-el-secreto-m%C3%A1s-perfumado-podr%C3%A1-se/25344967681849805/</t>
+          <t>https://www.facebook.com/perfilcom/posts/a-qu%C3%A9-hora-se-estren%C3%B3-en-netflix-la-segunda-parte-de-bridgerton-4-en-argentina/1353904796770185/</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1325,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/NetflixArg/videos/bridgerton-netflix/863898726412695/</t>
+          <t>https://www.facebook.com/ComfortUruguay/videos/las-flores-desaparecieron-de-manera-misteriosa-el-secreto-m%C3%A1s-perfumado-podr%C3%A1-se/893079166830234/</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1342,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/NetflixArg/videos/bridgerton-netflix/888088347102338/</t>
+          <t>https://www.facebook.com/photo.php?fbid=1140471294916091&amp;set=a.421318166831411&amp;id=100068596927356</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1359,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tvshowuy/posts/m%C3%A1s-oscura-y-melanc%C3%B3lica-detalles-de-la-temporada-4-de-bridgerton-y-cu%C3%A1ndo-se-es/1585824876351505/</t>
+          <t>https://www.facebook.com/lannistercomics/posts/atenci%C3%B3n-amantes-de-bridgerton-disponible-la-colecci%C3%B3n-completa-se-estreno-la-2d/5591876737525968/</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1376,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/perfilcom/posts/a-qu%C3%A9-hora-se-estren%C3%B3-en-netflix-la-segunda-parte-de-bridgerton-4-en-argentina/1353904796770185/</t>
+          <t>https://www.facebook.com/ComfortUruguay/</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1393,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ComfortUruguay/videos/las-flores-desaparecieron-de-manera-misteriosa-el-secreto-m%C3%A1s-perfumado-podr%C3%A1-se/893079166830234/</t>
+          <t>https://www.facebook.com/lannistercomics/posts/saga-de-g%C3%A9nero-romance-hist%C3%B3rico-los-bridgerton-escrita-por-julia-quinn-y-public/4591684954211823/</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1410,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/NetflixArg/videos/bridgerton-3-parte-2/448650128016965/</t>
+          <t>https://www.facebook.com/groups/769572330299468/posts/1727394321183926/</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1427,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/elpaisuy/posts/netflix-asegura-que-bridgerton-es-la-serie-m%C3%A1s-vista-de-toda-su-historia-la-prod/10160662759376754/</t>
+          <t>https://www.facebook.com/EmbajadaBritanicaMontevideo/posts/-ya-vieron-la-nueva-serie-de-netflix-queen-charlotte-si-bien-la-serie-ocurre-en-/577169867833684/</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1461,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/769572330299468/posts/1727394321183926/</t>
+          <t>https://www.facebook.com/elpaisuy/posts/netflix-asegura-que-bridgerton-es-la-serie-m%C3%A1s-vista-de-toda-su-historia-la-prod/10160662759376754/</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1478,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/elpaisuy/photos/netflix-revel%C3%B3-el-primer-adelanto-de-la-cuarta-temporada-de-bridgerton-y-confirm/1161703139424442/</t>
+          <t>https://www.facebook.com/NetflixArg/videos/bridgerton-3-parte-2/448650128016965/</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1495,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/redessocialesarg/videos/un-paseo-estilo-bridgerton-gratis-en-buenos-aires-s%C3%AD-est%C3%A1-pasandonetflix-organiz/926751779827211/</t>
+          <t>https://www.facebook.com/elpaisuy/photos/netflix-revel%C3%B3-el-primer-adelanto-de-la-cuarta-temporada-de-bridgerton-y-confirm/1161703139424442/</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1512,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/elpaisuy/posts/netflix-asegura-que-bridgerton-es-la-serie-m%C3%A1s-vista-de-toda-su-historia-la-prod/10160660939456754/</t>
+          <t>https://www.facebook.com/BridgertonLatinoamerica/posts/ay-ben-te-mmste-%EF%B8%8Fbridgerton-bridgertonnetflix-benedictbridgerton-netflix/1345480020959147/</t>
         </is>
       </c>
     </row>
@@ -1512,12 +1524,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chenetflix/video/7600424191522786573</t>
+          <t>https://www.facebook.com/redessocialesarg/videos/un-paseo-estilo-bridgerton-gratis-en-buenos-aires-s%C3%AD-est%C3%A1-pasandonetflix-organiz/926751779827211/</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1541,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@milakate1999/video/7606732930806729991</t>
+          <t>https://www.facebook.com/elpaisuy/posts/netflix-asegura-que-bridgerton-es-la-serie-m%C3%A1s-vista-de-toda-su-historia-la-prod/10160660939456754/</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1563,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@netflixlat/video/7593055754735865096</t>
+          <t>https://www.tiktok.com/@chenetflix/video/7600424191522786573</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1580,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@netflixlat/video/7602268274629397776</t>
+          <t>https://www.tiktok.com/@milakate1999/video/7606732930806729991</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1597,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chenetflix/video/7595703870014131469</t>
+          <t>https://www.tiktok.com/@netflixlat/video/7593055754735865096</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chenetflix/video/7609844795061652749</t>
+          <t>https://www.tiktok.com/@netflixlat/video/7602268274629397776</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1631,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@netflixes/video/7600447840447581462</t>
+          <t>https://www.tiktok.com/@chenetflix/video/7595703870014131469</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1648,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chenetflix/video/7595649570139344142</t>
+          <t>https://www.tiktok.com/@chenetflix/video/7609844795061652749</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1665,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@eugepuche/video/7611298973923495176</t>
+          <t>https://www.tiktok.com/@netflixes/video/7600447840447581462</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1682,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@pijama.surf/video/7600861625373035796</t>
+          <t>https://www.tiktok.com/@chenetflix/video/7595649570139344142</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1699,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/discover/cuando-sale-bridgerton-4-en-argentina</t>
+          <t>https://www.tiktok.com/@eugepuche/video/7611298973923495176</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1716,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@netflixlat/video/7369335819200449793</t>
+          <t>https://www.tiktok.com/discover/cuando-sale-bridgerton-4-en-argentina</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1733,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@netflixlat/video/7603930655117872404</t>
+          <t>https://www.tiktok.com/@netflixlat/video/7369335819200449793</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1750,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chenetflix/video/7598326974951607565</t>
+          <t>https://www.tiktok.com/@cpher_art/video/7609546888773127445</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1767,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chenetflix/video/7601155903466851598</t>
+          <t>https://www.tiktok.com/@netflixlat/video/7603930655117872404</t>
         </is>
       </c>
     </row>
@@ -1789,7 +1801,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cpher_art/video/7609546888773127445</t>
+          <t>https://www.tiktok.com/@marcoseyo/video/7601633663150722311</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1835,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@apasionadosxviajar/video/7609550112158764309</t>
+          <t>https://www.tiktok.com/@chulaenlaluna/video/7600849139949112583</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1852,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@marcoseyo/video/7601633663150722311</t>
+          <t>https://www.tiktok.com/@onlinemami_/video/7610200734360964360</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1869,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chulaenlaluna/video/7600849139949112583</t>
+          <t>https://www.tiktok.com/@chenetflix/video/7598326974951607565</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1886,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chenetflix/video/7358085398805007658</t>
+          <t>https://www.tiktok.com/@netflixes/video/7367679551809277216</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1903,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mariaspeaksenglish/video/7369691983713094945</t>
+          <t>https://www.tiktok.com/@chenetflix/video/7358085398805007658</t>
         </is>
       </c>
     </row>
@@ -1908,7 +1920,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@netflixes/video/7367679551809277216</t>
+          <t>https://www.tiktok.com/@alewkd/video/7367172113842654470</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1937,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@alewkd/video/7367172113842654470</t>
+          <t>https://www.tiktok.com/@adriianabad99/video/7601432071604702487</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1954,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/discover/bridgerton-argentina-victoria-resco</t>
+          <t>https://www.tiktok.com/@chenetflix/video/7606441973901233422</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1971,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chenetflix/video/7606441973901233422</t>
+          <t>https://www.tiktok.com/@hoyestaparaleer/video/7370405528113057029</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1988,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@adriianabad99/video/7601432071604702487</t>
+          <t>https://www.tiktok.com/@onlinemami_/video/7595735741922168082</t>
         </is>
       </c>
     </row>
@@ -1988,12 +2000,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@suny.jks/video/7603162089301003528</t>
+          <t>https://www.youtube.com/channel/UC5ZiUaIJ2b5dYBYGf5iEUrA</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2056,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=UsAEQwTAuH0</t>
+          <t>https://m.youtube.com/@LADSpanishTV-8386x/videos?view=0&amp;sort=dd&amp;shelf_id=2</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2073,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/hashtag/staircasescene</t>
+          <t>https://www.youtube.com/watch?v=kMXQlA14JBQ</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2090,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/c/aragondigital/channels</t>
+          <t>https://www.youtube.com/watch?v=UsAEQwTAuH0</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2102,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:youtube.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kMXQlA14JBQ</t>
+          <t>https://x.com/DebateUruguay_/status/2017275931405258915</t>
         </is>
       </c>
     </row>
@@ -2107,12 +2119,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:youtube.com</t>
+          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://m.youtube.com/@LADSpanishTV-8386x/videos?view=0&amp;sort=dd&amp;shelf_id=2</t>
+          <t>https://x.com/agusc4brera</t>
         </is>
       </c>
     </row>
@@ -2129,7 +2141,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://x.com/DebateUruguay_/status/2017275931405258915</t>
+          <t>https://x.com/elpaisuy/status/1344705160375894019</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2158,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://x.com/agusc4brera</t>
+          <t>https://x.com/vicky_oyhenart</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2175,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://x.com/elpaisuy/status/1344705160375894019</t>
+          <t>https://x.com/proximapaginaok</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2192,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://x.com/vicky_oyhenart</t>
+          <t>https://x.com/XimeCoonX</t>
         </is>
       </c>
     </row>
@@ -2197,7 +2209,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://x.com/proximapaginaok</t>
+          <t>https://x.com/nadia2abi</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2226,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://x.com/XimeCoonX</t>
+          <t>https://x.com/karenreiscach</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2243,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://x.com/nadia2abi</t>
+          <t>https://x.com/lizkocacomert</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2260,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://x.com/karenreiscach</t>
+          <t>https://x.com/NBonin/status/1797486263148396771</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2277,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://x.com/lizkocacomert</t>
+          <t>https://x.com/cruzher30</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2294,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://x.com/NBonin/status/1797486263148396771</t>
+          <t>https://x.com/__lavenderhaze</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2311,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://x.com/arissanchezzz</t>
+          <t>https://x.com/anto_z31</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://x.com/__lavenderhaze</t>
+          <t>https://x.com/itchytaglitter?lang=da</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2345,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://x.com/anto_z31</t>
+          <t>https://x.com/laboraton</t>
         </is>
       </c>
     </row>
@@ -2367,7 +2379,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://x.com/laboraton</t>
+          <t>https://x.com/mpazperalta</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2396,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://x.com/mpazperalta</t>
+          <t>https://x.com/Gala0374</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2430,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://x.com/Gala0374</t>
+          <t>https://x.com/puig_vero</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2447,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://x.com/puig_vero</t>
+          <t>https://x.com/arissanchezzz</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2481,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://x.com/newslinereport</t>
+          <t>https://x.com/lys_12</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2498,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://x.com/lecturasdeannie</t>
+          <t>https://x.com/florenciaamorin</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2515,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://x.com/MaugeGarcia</t>
+          <t>https://x.com/ddl_sophie97</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2532,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://x.com/florenciaamorin</t>
+          <t>https://x.com/lecturasdeannie</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2549,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://x.com/ddl_sophie97</t>
+          <t>https://x.com/Aurorakillian30</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2566,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>https://x.com/lys_12</t>
+          <t>https://x.com/Manuu_CYfan</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2583,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://x.com/Aurorakillian30</t>
+          <t>https://x.com/nazagaggero</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2600,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://x.com/Manuu_CYfan</t>
+          <t>https://x.com/newslinereport</t>
         </is>
       </c>
     </row>
@@ -2605,41 +2617,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://x.com/search?lang=es&amp;q=Sigue%20plataforma%20DUTT%20comentarios%202026%20usuarios%20reales.uns</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Bridgerton</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>https://x.com/nazagaggero</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Bridgerton</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>https://x.com/tartancrepes</t>
+          <t>https://x.com/IvanQuiroga_Ok</t>
         </is>
       </c>
     </row>

--- a/paginas_encontradas.xlsx
+++ b/paginas_encontradas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C129"/>
+  <dimension ref="A1:C135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,2176 +448,2278 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DVOdiylkRc-/</t>
+          <t>https://www.instagram.com/reel/DUisvo-jChN/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tctelevision/p/DVORrImDeBs/?hl=af</t>
+          <t>https://www.instagram.com/reel/DKabsuRy6Ab/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DVOz-rogGXC/</t>
+          <t>https://www.instagram.com/reel/DTVueIGCYHM/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DVOSgCPkZjd/</t>
+          <t>https://www.instagram.com/p/DTVjL6VDnQL/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DJrtQepMxwi/</t>
+          <t>https://www.instagram.com/p/DUoXh9pjysE/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DVMdRG4iYyX/</t>
+          <t>https://www.instagram.com/p/DTjLRtKjbcx/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DT3FlgNDvHR/</t>
+          <t>https://www.instagram.com/p/DTv7ZRCkRc4/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DVMpuBIgEgM/</t>
+          <t>https://www.instagram.com/p/DTZN-s3jNWz/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DVPLEs_DodX/</t>
+          <t>https://www.instagram.com/p/DQrfmq3jcGs/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DUHgZlgEQG_/</t>
+          <t>https://www.instagram.com/p/DTjno7ZjhBU/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DUPD4U9Dj3H/</t>
+          <t>https://www.instagram.com/p/DS5nJoLEVrj/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DUFea54DG6x/</t>
+          <t>https://www.instagram.com/p/DUEErQakZE5/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DVE-d1EibtV/</t>
+          <t>https://www.instagram.com/p/DUm3vtogEoX/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DSyG11PF-B4/</t>
+          <t>https://www.instagram.com/p/DTvXfDcgW7i/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DUGpQq-ET9_/</t>
+          <t>https://www.instagram.com/p/DS2nnk4kb4T/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DVPsr7HjUQR/</t>
+          <t>https://www.instagram.com/p/DTjUEEej23q/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DUJlHkvkbJu/</t>
+          <t>https://www.instagram.com/p/DUgSJBMkdsU/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DUUbJnADa1G/</t>
+          <t>https://www.instagram.com/p/DUohKr_D-fH/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DVST-buDMPt/</t>
+          <t>https://www.instagram.com/reel/DRf7Df0iPUS/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DSu-BlzEYzy/</t>
+          <t>https://www.instagram.com/reel/DTbqxbKAKZr/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DUGyD-6j4ls/</t>
+          <t>https://www.instagram.com/p/DTlWekdkab5/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DUlEx1NjaYZ/</t>
+          <t>https://www.instagram.com/p/DTLNyLXitno/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DS5geZTDU8R/</t>
+          <t>https://www.instagram.com/p/DSypREHjYfB/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DUJH2TEDHrY/</t>
+          <t>https://www.instagram.com/p/DTjNVQSDQJF/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DUUOAlgj70E/</t>
+          <t>https://www.instagram.com/p/DT_mvOClUuJ/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DStkvG1DEUY/</t>
+          <t>https://www.instagram.com/p/DTk_AH-jb2K/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:instagram.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DSvW5bUEsoO/</t>
+          <t>https://www.instagram.com/p/DTg48PPiLr5/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/NetflixArg/videos/bridgerton-netflix/874579312061852/</t>
+          <t>https://www.instagram.com/p/DTtDGgaiEKC/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/cadenadelmarfm1065/videos/bridgerton-netflix-4%C2%AA-temporada-arrasa-y-vuelve-a-cautivar-al-p%C3%BAblico/2171927366915739/</t>
+          <t>https://www.instagram.com/p/DTvKjQUjc0U/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ComfortUruguay/videos/una-nueva-pista-perfumada-llega-al-palacioel-secreto-est%C3%A1-a-punto-de-ser-revelad/1615445112706598/</t>
+          <t>https://www.instagram.com/p/DTgj_FSicOu/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:instagram.com</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/NetflixArg/videos/bridgerton-netflix/2378705162590136/</t>
+          <t>https://www.instagram.com/reel/DTP8FBDjl5B/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/cartasaeliza/posts/ya-sabes-a-qu%C3%A9-hora-estar%C3%A1n-disponibles-los-nuevos-episodios-de-bridgerton-estad/1512664910859722/</t>
+          <t>https://www.facebook.com/61566493452345/posts/la-reina-del-flow-3-estreno-oficial-netflix-y-que-dia-salver-m%C3%A1s/122177119484549781/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/769572330299468/posts/1762034177719940/</t>
+          <t>https://www.facebook.com/CaracolTVIntl/posts/el-fen%C3%B3meno-mundial-regresala-reina-del-flow-3-ya-est%C3%A1-disponible-con-sus-primer/1494031882731003/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/NetflixArg/videos/bridgerton-netflix/1472684427721945/</t>
+          <t>https://www.facebook.com/61566493452345/posts/la-reina-del-flow-3-estreno-oficial-en-netflix-y-avancver-m%C3%A1s/122165786636549781/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/NetflixArg/videos/bridgerton-netflix/742416995394439/</t>
+          <t>https://www.facebook.com/CaracolTVIntl/posts/el-flow-no-para-lareinadelflow3-se-mantiene-en-el-top-10-de-europa-y-am%C3%A9rica-lis/1520423473425177/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/debateuruguaynoticias/posts/baile-de-m%C3%A1scaras-y-taylor-swift-se-estren%C3%B3-la-cuarta-temporada-de-los-bridgerto/877969608319032/</t>
+          <t>https://www.facebook.com/cacorali/posts/el-14-de-enero-de-2026-se-estrena-en-netflix-la-reina-del-flow-3/1254500930067645/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/NetflixArg/videos/bridgerton-netflix/887334047385646/</t>
+          <t>https://www.facebook.com/LOS40Colombia/posts/te-contamos-httpslos40comco20260115cuando-se-estrenan-los-nuevos-episodios-de-la/944258211597340/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/NetflixArg/posts/este-es-el-evento-de-la-temporada-para-todos-los-fans-de-bridgertonel-9-de-febre/1330235185804528/</t>
+          <t>https://www.facebook.com/CaracolTVIntl/photos/el-flow-se-hace-sentir-en-todo-el-mundo-lareinadelflow3-est%C3%A1-presente-desde-el-d/1495420059258852/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/NetflixArg/videos/bridgerton-netflix/1242972931091091/</t>
+          <t>https://www.facebook.com/charlyflowof9/posts/faltan-3-d%C3%ADas-para-el-estreno-en-netflix-%EF%B8%8F-lareinadelflow/1211012641124597/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/elpaisuy/posts/de-bridgerton-a-la-odisea-de-nolan-y-hasta-una-pel%C3%ADcula-uruguaya-sobre-escritora/1232928072301948/</t>
+          <t>https://www.facebook.com/elpaisuy/posts/la-reina-del-flow-cinco-claves-para-un-%C3%A9xito-de-netflix-a-puro-reggaeton-y-traic/10161565616471754/?locale=ms_MY</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/vovediariodigital/posts/-la-espera-de-los-fan%C3%A1ticos-de-bridgerton-llega-a-su-fin-finalmente-este-jueves-/1219537233704696/</t>
+          <t>https://www.facebook.com/groups/1561085184508241/posts/1899323187351104/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/RTSmedios/photos/espect%C3%A1culos-netflix-revel%C3%B3-t%C3%ADtulos-y-duraci%C3%B3n-de-los-primeros-episodios-de-la-c/1369331881873630/</t>
+          <t>https://www.facebook.com/61566493452345/posts/la-reina-del-flow-3-cap%C3%ADtulo-1-el-regreso-de-charly-y-suver-m%C3%A1s/122191883432549781/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/clarincom/posts/la-cuarta-temporada-debuta-este-29-de-enero-en-netflix-para-desentra%C3%B1ar-el-inici/1341408221354182/</t>
+          <t>https://www.facebook.com/CaracolTVIntl/photos/el-flow-no-para-lareinadelflow3-se-mantiene-en-el-top-10-de-europa-y-am%C3%A9rica-lis/1520423456758512/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/photo.php?fbid=1747795425302901&amp;id=299859170096541&amp;set=a.299860116763113</t>
+          <t>https://www.facebook.com/107733597773339/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/libreriaelvirreyuy/posts/tras-la-exitosa-saga-bridgerton-que-netflix-ha-convertido-en-una-serie-llega-la-/2858888594376833/</t>
+          <t>https://www.facebook.com/groups/578566984666491/posts/897204959469357/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ElObservadorUY/posts/bridgerton-fue-una-de-las-series-m%C3%A1s-vistas-en-netflix-el-verano-pasado-en-urugu/10159849239625842/?locale=hi_IN</t>
+          <t>https://www.facebook.com/CaracolTVIntl/posts/yeimy-montoya-est%C3%A1-de-regreso-y-va-por-todo-la-temporada-3-de-la-reina-del-flow-/1494322319368626/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/elpaisuy/posts/netflix-revel%C3%B3-el-primer-adelanto-de-la-cuarta-temporada-de-bridgerton-y-confirm/1161703156091107/</t>
+          <t>https://www.facebook.com/CaracolTVIntl/posts/d%C3%ADa-1-el-a%C3%B1o-empieza-con-flow-conoce-todo-sobre-el-fen%C3%B3meno-mundial-en-content-a/1499538222180369/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/NetflixArg/videos/bridgerton-netflix/888088347102338/</t>
+          <t>https://www.facebook.com/groups/320209418102813/posts/9890587694398223/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tvshowuy/posts/m%C3%A1s-oscura-y-melanc%C3%B3lica-detalles-de-la-temporada-4-de-bridgerton-y-cu%C3%A1ndo-se-es/1585824876351505/</t>
+          <t>https://www.facebook.com/61566493452345/photos/la-reina-del-flow-3-avance-cap%C3%ADtulo-41-yeimver-m%C3%A1s/122203698758549781/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ComfortUruguay/videos/las-flores-desaparecieron-de-manera-misteriosa-el-secreto-m%C3%A1s-perfumado-podr%C3%A1-se/25344967681849805/</t>
+          <t>https://www.facebook.com/61566804145750/posts/la-reina-del-flow-3-cap%C3%ADtulo-1-fecha-de-estreno-cu%C3%A1ndo-salever-m%C3%A1s/122175081392560138/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/perfilcom/posts/a-qu%C3%A9-hora-se-estren%C3%B3-en-netflix-la-segunda-parte-de-bridgerton-4-en-argentina/1353904796770185/</t>
+          <t>https://www.facebook.com/cacorali/posts/hola-nuestra-gente-linda-y-bella-gracias-por-vernos-por-tanto-cari%C3%B1o-y-aprecio-p/1266496085534796/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ComfortUruguay/videos/las-flores-desaparecieron-de-manera-misteriosa-el-secreto-m%C3%A1s-perfumado-podr%C3%A1-se/893079166830234/</t>
+          <t>https://www.facebook.com/magacin247/posts/la-reina-del-flow-3-cap%C3%ADtulo-20-final-ya-est%C3%A1-en-netflixel-esperado-episodio-fin/1239260678401965/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/photo.php?fbid=1140471294916091&amp;set=a.421318166831411&amp;id=100068596927356</t>
+          <t>https://www.facebook.com/100091764826058/posts/only-four-days-to-go-until-yeimy-and-charly-light-up-our-screens-once-again-lare/829154900153330/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/lannistercomics/posts/atenci%C3%B3n-amantes-de-bridgerton-disponible-la-colecci%C3%B3n-completa-se-estreno-la-2d/5591876737525968/</t>
+          <t>https://www.facebook.com/elpaisuy/posts/estrella-de-una-de-las-series-latinas-m%C3%A1s-vistas-en-la-historia-de-netflix-viene/832496892345070/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ComfortUruguay/</t>
+          <t>https://www.facebook.com/61566493452345/posts/la-reina-del-flow-3-sky-se-enamora-de-charlver-m%C3%A1s/122192511440549781/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/lannistercomics/posts/saga-de-g%C3%A9nero-romance-hist%C3%B3rico-los-bridgerton-escrita-por-julia-quinn-y-public/4591684954211823/</t>
+          <t>https://www.facebook.com/Rapzadbarrio/posts/cuando-llegu%C3%A9-a-la-reina-del-flow-no-tra%C3%ADa-discursos-ni-promesas-tra%C3%ADa-tres-cap%C3%AD/1404652861030203/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/769572330299468/posts/1727394321183926/</t>
+          <t>https://www.facebook.com/Rapzadbarrio/posts/con-el-coraz%C3%B3n-lleno-de-felicidad-le-digo-a-todos-los-seguidores-de-la-reina-del/1411391973689625/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/EmbajadaBritanicaMontevideo/posts/-ya-vieron-la-nueva-serie-de-netflix-queen-charlotte-si-bien-la-serie-ocurre-en-/577169867833684/</t>
+          <t>https://www.facebook.com/p/fanscarocaliuy-100064626826536/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/NetflixArg/videos/bridgerton-3-parte-2/464109322937601/</t>
+          <t>https://www.facebook.com/photo.php?fbid=1233121625538909&amp;set=a.419824346868645&amp;id=100065232504372</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/elpaisuy/posts/netflix-asegura-que-bridgerton-es-la-serie-m%C3%A1s-vista-de-toda-su-historia-la-prod/10160662759376754/</t>
+          <t>https://www.facebook.com/61566493452345/posts/la-reina-del-flow-3-cap%C3%ADtulo-2-la-hija-de-los-reyes-del-flver-m%C3%A1s/122165789336549781/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:facebook.com</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/NetflixArg/videos/bridgerton-3-parte-2/448650128016965/</t>
+          <t>https://www.facebook.com/carocalimx1/posts/deja-tu-opini%C3%B3n-si-anticipas-con-entusiasmo-la-llegada-del-13-de-enero-de-2026-p/863246672966629/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/elpaisuy/photos/netflix-revel%C3%B3-el-primer-adelanto-de-la-cuarta-temporada-de-bridgerton-y-confirm/1161703139424442/</t>
+          <t>https://www.tiktok.com/@_lorenaamartiin_/video/7586754744983588118</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/BridgertonLatinoamerica/posts/ay-ben-te-mmste-%EF%B8%8Fbridgerton-bridgertonnetflix-benedictbridgerton-netflix/1345480020959147/</t>
+          <t>https://www.tiktok.com/@karolinesita/video/7603443290523880726</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/redessocialesarg/videos/un-paseo-estilo-bridgerton-gratis-en-buenos-aires-s%C3%AD-est%C3%A1-pasandonetflix-organiz/926751779827211/</t>
+          <t>https://www.tiktok.com/@kiarareina16/video/7601552624520940822</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:facebook.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/elpaisuy/posts/netflix-asegura-que-bridgerton-es-la-serie-m%C3%A1s-vista-de-toda-su-historia-la-prod/10160660939456754/</t>
+          <t>https://www.tiktok.com/@ceciliafernandez222/video/7596311763830738188</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chenetflix/video/7600424191522786573</t>
+          <t>https://www.tiktok.com/discover/cuando-se-estrena-la-reina-del-flow-3-en-netflix-en-uruguay</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@milakate1999/video/7606732930806729991</t>
+          <t>https://www.tiktok.com/discover/cuando-se-estrena-la-reina-del-flow-3-en-uruguay</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@netflixlat/video/7593055754735865096</t>
+          <t>https://www.tiktok.com/@carlos1torres1chile/video/7448310383439400198</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@netflixlat/video/7602268274629397776</t>
+          <t>https://www.tiktok.com/discover/cu%C3%A1ndo-sale-la-reina-del-flow-en-uruguay</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chenetflix/video/7595703870014131469</t>
+          <t>https://www.tiktok.com/discover/la-reina-del-flow-3-estreno-fecha-2025-en-netflix</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chenetflix/video/7609844795061652749</t>
+          <t>https://www.tiktok.com/@aura.series/photo/7595330636265671944?lang=tr-TR</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@netflixes/video/7600447840447581462</t>
+          <t>https://www.tiktok.com/@caracoltv/video/7594237575699729671</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chenetflix/video/7595649570139344142</t>
+          <t>https://www.tiktok.com/@carlos1torres1chile/video/7454264991202544901</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@eugepuche/video/7611298973923495176</t>
+          <t>https://www.tiktok.com/discover/cuando-estrena-la-reina-del-flow-3-en-magi</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/discover/cuando-sale-bridgerton-4-en-argentina</t>
+          <t>https://www.tiktok.com/discover/netflix-confirma-la-reina-del-flow-3-vienen-a-costa-rica</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@netflixlat/video/7369335819200449793</t>
+          <t>https://www.tiktok.com/discover/ya-sali%C3%B3-la-reina-del-flow-en-netflix-de-brasil</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cpher_art/video/7609546888773127445</t>
+          <t>https://www.tiktok.com/discover/cuando-sale-la-reina-del-flow-3-en-uruguay</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@netflixlat/video/7603930655117872404</t>
+          <t>https://www.tiktok.com/@caracoltvintl/video/7593403712970919175</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@topic.media/video/7394894841613683973</t>
+          <t>https://www.tiktok.com/@janibejaranonews/video/7592820334475152660</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@marcoseyo/video/7601633663150722311</t>
+          <t>https://www.tiktok.com/discover/a-qu%C3%A9-hora-se-estrena-la-reina-del-flow-en-netflix</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chenetflix/video/7610098651112705294</t>
+          <t>https://www.tiktok.com/discover/cuando-sale-la-reina-del-flow-3-de-2025</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chulaenlaluna/video/7600849139949112583</t>
+          <t>https://www.tiktok.com/discover/cuando-se-estrena-la-reina-del-flow-3-en-ecuador</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@onlinemami_/video/7610200734360964360</t>
+          <t>https://www.tiktok.com/@carlostorresfanpage/video/7573028963681881366</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chenetflix/video/7598326974951607565</t>
+          <t>https://www.tiktok.com/discover/cuando-sale-la-3-temporada-de-la-reina-del-flow-en-uruguay</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@netflixes/video/7367679551809277216</t>
+          <t>https://www.tiktok.com/discover/la-reina-del-flow-3-ya-esta-en-netflix</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chenetflix/video/7358085398805007658</t>
+          <t>https://www.tiktok.com/@noticiascaracol/video/7594960668655226123</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@alewkd/video/7367172113842654470</t>
+          <t>https://www.tiktok.com/@aleperu_/video/7595177348345924871</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@adriianabad99/video/7601432071604702487</t>
+          <t>https://www.tiktok.com/discover/cuando-se-estrena-la-reina-del-flow-3-en-argentina-netflix</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chenetflix/video/7606441973901233422</t>
+          <t>https://www.tiktok.com/discover/cuando-sale-en-netflix-la-reina-de-flow</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@hoyestaparaleer/video/7370405528113057029</t>
+          <t>https://www.tiktok.com/@charleimy.fr/video/7586830899900189974</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:tiktok.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@onlinemami_/video/7595735741922168082</t>
+          <t>https://www.tiktok.com/discover/a-que-hora-sale-la-reina-del-flow-3-en-netflix</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:youtube.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UC5ZiUaIJ2b5dYBYGf5iEUrA</t>
+          <t>https://www.tiktok.com/discover/como-encuentro-en-netflix-los-capitulos-de-la-reina-del-flow</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:youtube.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IAqV-7F-brg</t>
+          <t>https://www.tiktok.com/@aura.series/photo/7595330636265671944?lang=hu-HU</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:youtube.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:tiktok.com</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=0NSWp5airvo</t>
+          <t>https://www.tiktok.com/@la.reina.del.flowoficial/video/7280343680286805254</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:youtube.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://m.youtube.com/@LADSpanishTV-8386x/videos?view=0&amp;sort=dd&amp;shelf_id=2</t>
+          <t>https://www.youtube.com/watch?v=hQRTiLbQo8I</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:youtube.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kMXQlA14JBQ</t>
+          <t>https://www.youtube.com/watch?v=941-adg1sbc</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:youtube.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=UsAEQwTAuH0</t>
+          <t>https://www.youtube.com/watch?v=8_HjNe13fTA</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://x.com/DebateUruguay_/status/2017275931405258915</t>
+          <t>https://www.youtube.com/playlist?list=PLL485KLzcXN5JWXwILq4HkDIkEgqVVTJI</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://x.com/agusc4brera</t>
+          <t>https://m.youtube.com/watch?v=MB_9VOgsQCo</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://x.com/elpaisuy/status/1344705160375894019</t>
+          <t>https://www.youtube.com/watch?v=d-HB1_e67hw</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://x.com/vicky_oyhenart</t>
+          <t>https://www.youtube.com/watch?v=d-HB1_e67hw&amp;t=0</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://x.com/proximapaginaok</t>
+          <t>https://www.youtube.com/watch?v=d-HB1_e67hw&amp;t=125</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://x.com/XimeCoonX</t>
+          <t>https://www.youtube.com/watch?v=d-HB1_e67hw&amp;t=173</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://x.com/nadia2abi</t>
+          <t>https://www.youtube.com/watch?v=d-HB1_e67hw&amp;t=410</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://x.com/karenreiscach</t>
+          <t>https://www.youtube.com/watch?v=d-HB1_e67hw&amp;t=497</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://x.com/lizkocacomert</t>
+          <t>https://www.youtube.com/watch?v=d-HB1_e67hw&amp;t=861</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://x.com/NBonin/status/1797486263148396771</t>
+          <t>https://www.youtube.com/watch?v=d-HB1_e67hw&amp;t=1060</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://x.com/cruzher30</t>
+          <t>https://www.youtube.com/watch?v=d-HB1_e67hw&amp;t=1200</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://x.com/__lavenderhaze</t>
+          <t>https://www.youtube.com/watch?v=d-HB1_e67hw&amp;t=1303</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://x.com/anto_z31</t>
+          <t>https://www.youtube.com/watch?v=d-HB1_e67hw&amp;t=1450</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://x.com/itchytaglitter?lang=da</t>
+          <t>https://www.youtube.com/watch?v=d-HB1_e67hw&amp;t=1740</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://x.com/laboraton</t>
+          <t>https://www.youtube.com/watch?v=d-HB1_e67hw&amp;t=1944</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://x.com/feer__olvv</t>
+          <t>https://www.youtube.com/watch?v=d-HB1_e67hw&amp;t=2043</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://x.com/mpazperalta</t>
+          <t>https://www.youtube.com/watch?v=d-HB1_e67hw&amp;t=2310</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://x.com/Gala0374</t>
+          <t>https://www.youtube.com/watch?v=d-HB1_e67hw&amp;t=2550</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://x.com/Jotadangz</t>
+          <t>https://www.youtube.com/watch?v=d-HB1_e67hw&amp;t=2714</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://x.com/puig_vero</t>
+          <t>https://www.youtube.com/watch?v=d-HB1_e67hw&amp;t=3035</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://x.com/arissanchezzz</t>
+          <t>https://www.youtube.com/watch?v=d-HB1_e67hw&amp;t=3235</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://x.com/search?q=%23OCCH%C4%B0AM%C4%B0N&amp;src=typed_query</t>
+          <t>https://www.youtube.com/watch?v=d-HB1_e67hw&amp;t=3253</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://x.com/lys_12</t>
+          <t>https://www.youtube.com/watch?v=d-HB1_e67hw&amp;t=3497</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://x.com/florenciaamorin</t>
+          <t>https://www.youtube.com/watch?v=d-HB1_e67hw&amp;t=3787</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://x.com/ddl_sophie97</t>
+          <t>https://www.youtube.com/watch?v=d-HB1_e67hw&amp;t=3951</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://x.com/lecturasdeannie</t>
+          <t>https://www.youtube.com/watch?v=d-HB1_e67hw&amp;t=4208</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://x.com/Aurorakillian30</t>
+          <t>https://www.youtube.com/watch?v=d-HB1_e67hw&amp;t=4260</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>https://x.com/Manuu_CYfan</t>
+          <t>https://www.youtube.com/watch?v=Ga_WAsfzzAA</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://x.com/nazagaggero</t>
+          <t>https://m.youtube.com/@jrukc</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://x.com/newslinereport</t>
+          <t>https://www.youtube.com/watch?v=Bu7VDlvBvpk</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Bridgerton</t>
+          <t>la reina del flow</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>"Bridgerton" Netflix Uruguay site:x.com</t>
+          <t>"la reina del flow" Netflix Uruguay site:youtube.com</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://x.com/IvanQuiroga_Ok</t>
+          <t>https://www.youtube.com/watch?v=rYVTrL8FCao</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>la reina del flow</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>"la reina del flow" Netflix Uruguay site:x.com</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>https://x.com/prensario</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>la reina del flow</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>"la reina del flow" Netflix Uruguay site:x.com</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>https://x.com/miguelsmirnoff</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>la reina del flow</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>"la reina del flow" Netflix Uruguay site:x.com</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>https://x.com/VickyFraRu</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>la reina del flow</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>"la reina del flow" Netflix Uruguay site:x.com</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>https://x.com/yuryosma?lang=ha</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>la reina del flow</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>"la reina del flow" Netflix Uruguay site:x.com</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>https://x.com/arissanchezzz</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>la reina del flow</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>"la reina del flow" Netflix Uruguay site:x.com</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>https://x.com/Maaru_Caano</t>
         </is>
       </c>
     </row>
